--- a/314e-ig/output/ValueSet-servicerequest-category-314e.xlsx
+++ b/314e-ig/output/ValueSet-servicerequest-category-314e.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
